--- a/Manuscript/Figures_for_Manuscript_files/saved_png/Supp.xlsx
+++ b/Manuscript/Figures_for_Manuscript_files/saved_png/Supp.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="63">
   <si>
     <t xml:space="preserve">Chap1: beta diversity, pairwise</t>
   </si>
@@ -35,20 +36,196 @@
   </si>
   <si>
     <t xml:space="preserve">Accounting for LP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chap2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAA w.r.t LP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stderr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N.not.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acinetobacter_baumannii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escherichia_coli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variovorax_sp._RA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variovorax_paradoxus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klebsiella_quasipneumoniae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stenotrophomonas_maltophilia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brevundimonas_sp._DS20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calothrix_sp._NIES.3974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shigella_flexneri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrogenophaga_taeniospiralis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brevundimonas_fontaquae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variovorax_sp._PBL.H6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variovorax_sp._SRS16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variovorax_sp._PAMC_28711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fischerella_sp._NIES.3754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cyanobacterium_endosymbiont_of_Epithemia_turgida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escherichia_albertii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingomonas_panacisoli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingomonas_sp._FARSPH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salmonella_enterica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingomonas_sp._S2.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingomonas_koreensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escherichia_fergusonii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingomonas_sinipercae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acidovorax_sp._KKS102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingomonas_suaedae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhodoferax_koreense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thermoleptolyngbya_sp._PKUAC.SCTB121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roseateles_amylovorans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOOD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingomonas_alpina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delftia_acidovorans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingomonas_sp._QA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phyllobacterium_sp._T1018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fischerella_sp._JS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croceicoccus_sp._YJ47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variovorax_sp._PBL.E5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acidovorax_carolinensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variovorax_sp._PMC12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calothrix_sp._336.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dolichospermum_flos.aquae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nostoc_sp._MS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhodoferax_sp._GW822.FHT02A01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingomonas_endolithica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shigella_boydii</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00E+00"/>
   </numFmts>
   <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -69,6 +246,7 @@
       <sz val="10"/>
       <name val="Courier New"/>
       <family val="3"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -113,13 +291,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -249,72 +435,72 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>0.002</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>0.0001</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="2" t="n">
         <v>0.0013</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -327,4 +513,1481 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>2.03554842627889</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.0484484464833779</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>2.8425181253039E-015</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1.97270757896091E-012</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0.921662350544331</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.04966790469928</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>9.75342765932603E-011</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>3.38443939778613E-008</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>-3.39149279705819</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.229769364882277</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1.68360045972696E-009</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>3.89472906350169E-007</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>-3.19580343854298</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.259171310279819</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1.50704184527379E-008</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>2.61471760155002E-006</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>-0.766436200678925</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>0.073616086818163</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>1.12498913563331E-007</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>1.1893786371499E-005</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>-0.639318485742424</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>0.060556903589545</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>9.55576688732331E-008</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>1.1893786371499E-005</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>3.81148972130375</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>0.368110656289552</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>1.19966144957483E-007</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>1.1893786371499E-005</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>-2.12760594700637</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>0.222488878043511</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>3.01496379293157E-007</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>2.61548109036814E-005</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>3.31815183132703</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>0.362898101901437</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>5.03256238863041E-007</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>3.88066477523278E-005</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>-3.23165310923982</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>0.358081616134054</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>5.83595233433058E-007</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>4.05015092002542E-005</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>2.42946874757561</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>0.284012489662603</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1.06623421356753E-006</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>6.72696858378063E-005</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>-2.57599012180562</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>0.328749338087185</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>2.80436277024324E-006</v>
+      </c>
+      <c r="I15" s="0" t="n">
+        <v>0.000162185646879068</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>-2.51953877383423</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>0.36215788996766</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>9.96146072419514E-006</v>
+      </c>
+      <c r="I16" s="0" t="n">
+        <v>0.00053178874943011</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>-3.0323154717027</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>0.492245732122077</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>3.43122543349245E-005</v>
+      </c>
+      <c r="I17" s="0" t="n">
+        <v>0.0017009074648884</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>-2.41745356288511</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>0.399836526035275</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>4.12497516120456E-005</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <v>0.00190848850791731</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>-2.02073689695941</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>0.340396650164552</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>4.93250495451147E-005</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <v>0.00213947402401935</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>2.24473644610638</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>0.410837990224907</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>0.000108635079484598</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>0.00443486736248887</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>-0.993687874926557</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>0.185882084098689</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>0.000132951123147912</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>0.00512600441470282</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>-0.987254843069378</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>0.19247654304813</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>0.000193577696755945</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>0.00707068008150661</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>2.3219097547748</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>0.455300453731415</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>0.000203839119998027</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>0.00707321746393155</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>-1.80073789040321</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>0.365280202410378</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>0.000275153329553874</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>0.00909316241478042</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>-1.71967153863296</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>0.395637269791286</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>0.000791975924484813</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>0.0238970126779331</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>2.19418601391856</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>0.503753385684628</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>0.000778790606182561</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>0.0238970126779331</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>2.39789340597254</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>0.554667475288224</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" s="0" t="n">
+        <v>0.00082709791841563</v>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>0.0239169148075186</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>-1.71101019241411</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>0.398285711611776</v>
+      </c>
+      <c r="F28" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G28" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="H28" s="0" t="n">
+        <v>0.000869796776477753</v>
+      </c>
+      <c r="I28" s="0" t="n">
+        <v>0.0241455585150224</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>-1.93618920251031</v>
+      </c>
+      <c r="E29" s="0" t="n">
+        <v>0.490643490005679</v>
+      </c>
+      <c r="F29" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G29" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="H29" s="0" t="n">
+        <v>0.00167342443445489</v>
+      </c>
+      <c r="I29" s="0" t="n">
+        <v>0.0446675599042958</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>-2.01394607004982</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <v>0.524313738180343</v>
+      </c>
+      <c r="F30" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G30" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H30" s="0" t="n">
+        <v>0.0020416598537892</v>
+      </c>
+      <c r="I30" s="0" t="n">
+        <v>0.0524782199455446</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>-1.39625442054529</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>0.375890960985829</v>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" s="0" t="n">
+        <v>0.00259716347489865</v>
+      </c>
+      <c r="I31" s="0" t="n">
+        <v>0.0621528086751608</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>1.35559570707653</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <v>0.363314406703929</v>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" s="0" t="n">
+        <v>0.00251597369635755</v>
+      </c>
+      <c r="I32" s="0" t="n">
+        <v>0.0621528086751608</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>-1.83614639249259</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>0.515058309936583</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H33" s="0" t="n">
+        <v>0.00345618638905371</v>
+      </c>
+      <c r="I33" s="0" t="n">
+        <v>0.0799531118001092</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>-1.96288789470847</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>0.554477744261172</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="H34" s="0" t="n">
+        <v>0.00362473044822178</v>
+      </c>
+      <c r="I34" s="0" t="n">
+        <v>0.0811471913247069</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>-0.936056474798393</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <v>0.267528669614118</v>
+      </c>
+      <c r="F35" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H35" s="0" t="n">
+        <v>0.00392229915764647</v>
+      </c>
+      <c r="I35" s="0" t="n">
+        <v>0.0850648629814579</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>-2.24452937024223</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>0.655839525271536</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G36" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="H36" s="0" t="n">
+        <v>0.00454279742837481</v>
+      </c>
+      <c r="I36" s="0" t="n">
+        <v>0.0927265122144741</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>-2.08494400619399</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <v>0.607325441093099</v>
+      </c>
+      <c r="F37" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G37" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H37" s="0" t="n">
+        <v>0.00445111007106133</v>
+      </c>
+      <c r="I37" s="0" t="n">
+        <v>0.0927265122144741</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>-0.720815038708019</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <v>0.221287284209553</v>
+      </c>
+      <c r="F38" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G38" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" s="0" t="n">
+        <v>0.00623907600453591</v>
+      </c>
+      <c r="I38" s="0" t="n">
+        <v>0.123711964204226</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>-0.718534099614428</v>
+      </c>
+      <c r="E39" s="0" t="n">
+        <v>0.222488878043511</v>
+      </c>
+      <c r="F39" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G39" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H39" s="0" t="n">
+        <v>0.00658257502857799</v>
+      </c>
+      <c r="I39" s="0" t="n">
+        <v>0.126897418606476</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>1.34171864553419</v>
+      </c>
+      <c r="E40" s="0" t="n">
+        <v>0.433458259668638</v>
+      </c>
+      <c r="F40" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G40" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="H40" s="0" t="n">
+        <v>0.00852219630535607</v>
+      </c>
+      <c r="I40" s="0" t="n">
+        <v>0.15833159416758</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>-1.33786063262112</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <v>0.433458259668638</v>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="H41" s="0" t="n">
+        <v>0.00866945328295105</v>
+      </c>
+      <c r="I41" s="0" t="n">
+        <v>0.15833159416758</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>1.11140371218556</v>
+      </c>
+      <c r="E42" s="0" t="n">
+        <v>0.36215788996766</v>
+      </c>
+      <c r="F42" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="H42" s="0" t="n">
+        <v>0.00896889467960536</v>
+      </c>
+      <c r="I42" s="0" t="n">
+        <v>0.159600330965285</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>1.39602112990679</v>
+      </c>
+      <c r="E43" s="0" t="n">
+        <v>0.464541021261391</v>
+      </c>
+      <c r="F43" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G43" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H43" s="0" t="n">
+        <v>0.0101377538077072</v>
+      </c>
+      <c r="I43" s="0" t="n">
+        <v>0.175890028563719</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>0.679803786780401</v>
+      </c>
+      <c r="E44" s="0" t="n">
+        <v>0.229769364882277</v>
+      </c>
+      <c r="F44" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G44" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>0.0110863499796314</v>
+      </c>
+      <c r="I44" s="0" t="n">
+        <v>0.18765675331376</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>-1.31576128662261</v>
+      </c>
+      <c r="E45" s="0" t="n">
+        <v>0.464541021261391</v>
+      </c>
+      <c r="F45" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G45" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H45" s="0" t="n">
+        <v>0.014125759946708</v>
+      </c>
+      <c r="I45" s="0" t="n">
+        <v>0.218922963927496</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>0.973331127663267</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <v>0.345105578323946</v>
+      </c>
+      <c r="F46" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G46" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H46" s="0" t="n">
+        <v>0.0144543431101864</v>
+      </c>
+      <c r="I46" s="0" t="n">
+        <v>0.218922963927496</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>-1.51318607754027</v>
+      </c>
+      <c r="E47" s="0" t="n">
+        <v>0.539052445113134</v>
+      </c>
+      <c r="F47" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G47" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="H47" s="0" t="n">
+        <v>0.0148261949633895</v>
+      </c>
+      <c r="I47" s="0" t="n">
+        <v>0.218922963927496</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="0" t="n">
+        <v>-1.20853159056612</v>
+      </c>
+      <c r="E48" s="0" t="n">
+        <v>0.42931390945019</v>
+      </c>
+      <c r="F48" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G48" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="H48" s="0" t="n">
+        <v>0.0146033869586554</v>
+      </c>
+      <c r="I48" s="0" t="n">
+        <v>0.218922963927496</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" s="0" t="n">
+        <v>-0.979894953410964</v>
+      </c>
+      <c r="E49" s="0" t="n">
+        <v>0.34297970725969</v>
+      </c>
+      <c r="F49" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G49" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="H49" s="0" t="n">
+        <v>0.0134747584507537</v>
+      </c>
+      <c r="I49" s="0" t="n">
+        <v>0.218922963927496</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>-1.06337658595156</v>
+      </c>
+      <c r="E50" s="0" t="n">
+        <v>0.373050595903728</v>
+      </c>
+      <c r="F50" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G50" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" s="0" t="n">
+        <v>0.01364416866133</v>
+      </c>
+      <c r="I50" s="0" t="n">
+        <v>0.218922963927496</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="0" t="n">
+        <v>1.48927655865968</v>
+      </c>
+      <c r="E51" s="0" t="n">
+        <v>0.533886493383177</v>
+      </c>
+      <c r="F51" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G51" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H51" s="0" t="n">
+        <v>0.0153347822032513</v>
+      </c>
+      <c r="I51" s="0" t="n">
+        <v>0.221715392688675</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="0" t="n">
+        <v>1.79112794489095</v>
+      </c>
+      <c r="E52" s="0" t="n">
+        <v>0.656500554469488</v>
+      </c>
+      <c r="F52" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G52" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" s="0" t="n">
+        <v>0.0172377738082827</v>
+      </c>
+      <c r="I52" s="0" t="n">
+        <v>0.244143163733637</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/Manuscript/Figures_for_Manuscript_files/saved_png/Supp.xlsx
+++ b/Manuscript/Figures_for_Manuscript_files/saved_png/Supp.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9073" uniqueCount="842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9083" uniqueCount="850">
   <si>
     <t xml:space="preserve">Chap1: beta diversity, pairwise</t>
   </si>
@@ -2530,12 +2530,27 @@
     <t xml:space="preserve">df</t>
   </si>
   <si>
+    <t xml:space="preserve">asymp.LCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asymp.UCL</t>
+  </si>
+  <si>
     <t xml:space="preserve">z.ratio</t>
   </si>
   <si>
     <t xml:space="preserve">p.value</t>
   </si>
   <si>
+    <t xml:space="preserve">IRR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Buffer - Paraffin</t>
   </si>
   <si>
@@ -2551,17 +2566,25 @@
     <t xml:space="preserve">Shannon Index</t>
   </si>
   <si>
+    <t xml:space="preserve">lower.CL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upper.CL</t>
+  </si>
+  <si>
     <t xml:space="preserve">t.ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00E+00"/>
-    <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -2641,7 +2664,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2662,7 +2685,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -75216,7 +75251,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.15"/>
@@ -75251,10 +75286,25 @@
       <c r="F3" s="1" t="s">
         <v>835</v>
       </c>
+      <c r="G3" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>838</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>-0.21378455572476</v>
@@ -75263,18 +75313,33 @@
         <v>0.0894764134596816</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="E4" s="1" t="n">
+        <v>-0.423490478553591</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>-0.00407863289592919</v>
+      </c>
+      <c r="G4" s="0" t="n">
         <v>-2.38928391805838</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="H4" s="0" t="n">
         <v>0.0445043478393304</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>0.807522342348741</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>0.654757409874344</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>0.995929673430565</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0.277747536598157</v>
@@ -75283,18 +75348,33 @@
         <v>0.110932998069</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="E5" s="1" t="n">
+        <v>0.0177538038060954</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0.537741269390218</v>
+      </c>
+      <c r="G5" s="0" t="n">
         <v>2.50374137031255</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="H5" s="0" t="n">
         <v>0.0329083623942075</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>1.32015286485054</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>1.01791233939444</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>1.71213523908149</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>0.491532092322917</v>
@@ -75303,18 +75383,33 @@
         <v>0.12455795759674</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="E6" s="1" t="n">
+        <v>0.199605533875547</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.783458650770287</v>
+      </c>
+      <c r="G6" s="0" t="n">
         <v>3.94621188245769</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="H6" s="6" t="n">
         <v>0.000234218083580817</v>
       </c>
+      <c r="I6" s="0" t="n">
+        <v>1.63481899585685</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>1.22092105116255</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>2.18903027895992</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>840</v>
+      <c r="A8" s="4" t="s">
+        <v>845</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -75331,89 +75426,140 @@
         <v>833</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>835</v>
+        <v>847</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>-0.0147928662647929</v>
+        <v>841</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>0.000769549455383978</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>0.112628501803551</v>
+        <v>0.0123767211240244</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>239</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>-0.131342120581476</v>
+        <v>-0.0284198248706505</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.990534967649727</v>
+        <v>0.0299589237814185</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>0.0621771669307638</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>0.997870868830836</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>1.00076984563454</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>0.971980219662087</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>1.03041220764715</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.148844914842283</v>
+        <v>-0.0175056285499866</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>0.139104085560254</v>
+        <v>0.0150817030740411</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>239</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>1.07002547224114</v>
+        <v>-0.0530744574902919</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.53361372055903</v>
+        <v>0.0180632003903188</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>-1.16071961263563</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>0.47786864399406</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>0.982646704773411</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>0.948309401115531</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>1.01822732672077</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.163637781107076</v>
+        <v>-0.0182751780053705</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>0.156087043857442</v>
+        <v>0.0175274712408373</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>239</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>1.04837516979648</v>
+        <v>-0.0596121293603225</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.547143777052765</v>
+        <v>0.0230617733495814</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>-1.04265913515186</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>0.550726684584814</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <v>0.981890800427111</v>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>0.942129887246715</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <v>1.02332975210129</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="n">
-        <f aca="false">EXP(B4)</f>
-        <v>0.807522342348741</v>
-      </c>
+      <c r="B14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="n">
-        <f aca="false">EXP(B5)</f>
-        <v>1.32015286485054</v>
-      </c>
+      <c r="B15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5" t="n">
-        <f aca="false">EXP(B6)</f>
-        <v>1.63481899585685</v>
-      </c>
+      <c r="B16" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manuscript/Figures_for_Manuscript_files/saved_png/Supp.xlsx
+++ b/Manuscript/Figures_for_Manuscript_files/saved_png/Supp.xlsx
@@ -15,6 +15,8 @@
     <sheet name="T5" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Chap1_DAA" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Chap1_Alpha" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Chap1_beta" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Sheet9" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9083" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9098" uniqueCount="861">
   <si>
     <t xml:space="preserve">Chap1: beta diversity, pairwise</t>
   </si>
@@ -2576,6 +2578,39 @@
   </si>
   <si>
     <t xml:space="preserve">exp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dbrda(bray_dist ~ Control_type + Person + Year + Quarter, data = df_meta) with anova(…, by = “margin”)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Df</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SumOfSqs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omega2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pr(&gt;F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual</t>
   </si>
 </sst>
 </file>
@@ -2664,7 +2699,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2685,11 +2720,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2697,7 +2728,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -75286,19 +75317,19 @@
       <c r="F3" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="1" t="s">
         <v>840</v>
       </c>
     </row>
@@ -75321,19 +75352,19 @@
       <c r="F4" s="1" t="n">
         <v>-0.00407863289592919</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="5" t="n">
         <v>-2.38928391805838</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="5" t="n">
         <v>0.0445043478393304</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="5" t="n">
         <v>0.807522342348741</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="5" t="n">
         <v>0.654757409874344</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="5" t="n">
         <v>0.995929673430565</v>
       </c>
     </row>
@@ -75356,19 +75387,19 @@
       <c r="F5" s="1" t="n">
         <v>0.537741269390218</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="5" t="n">
         <v>2.50374137031255</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="5" t="n">
         <v>0.0329083623942075</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="5" t="n">
         <v>1.32015286485054</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="5" t="n">
         <v>1.01791233939444</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="5" t="n">
         <v>1.71213523908149</v>
       </c>
     </row>
@@ -75391,19 +75422,19 @@
       <c r="F6" s="3" t="n">
         <v>0.783458650770287</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="5" t="n">
         <v>3.94621188245769</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="3" t="n">
         <v>0.000234218083580817</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="5" t="n">
         <v>1.63481899585685</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="5" t="n">
         <v>1.22092105116255</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="5" t="n">
         <v>2.18903027895992</v>
       </c>
     </row>
@@ -75431,19 +75462,19 @@
       <c r="F9" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="1" t="s">
         <v>840</v>
       </c>
     </row>
@@ -75451,7 +75482,7 @@
       <c r="A10" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="6" t="n">
         <v>0.000769549455383978</v>
       </c>
       <c r="C10" s="1" t="n">
@@ -75466,19 +75497,19 @@
       <c r="F10" s="1" t="n">
         <v>0.0299589237814185</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="5" t="n">
         <v>0.0621771669307638</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="5" t="n">
         <v>0.997870868830836</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="5" t="n">
         <v>1.00076984563454</v>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="J10" s="5" t="n">
         <v>0.971980219662087</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="K10" s="5" t="n">
         <v>1.03041220764715</v>
       </c>
     </row>
@@ -75501,19 +75532,19 @@
       <c r="F11" s="1" t="n">
         <v>0.0180632003903188</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="5" t="n">
         <v>-1.16071961263563</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="5" t="n">
         <v>0.47786864399406</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="5" t="n">
         <v>0.982646704773411</v>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="J11" s="5" t="n">
         <v>0.948309401115531</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11" s="5" t="n">
         <v>1.01822732672077</v>
       </c>
     </row>
@@ -75536,30 +75567,30 @@
       <c r="F12" s="1" t="n">
         <v>0.0230617733495814</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="5" t="n">
         <v>-1.04265913515186</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="5" t="n">
         <v>0.550726684584814</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="I12" s="5" t="n">
         <v>0.981890800427111</v>
       </c>
-      <c r="J12" s="0" t="n">
+      <c r="J12" s="5" t="n">
         <v>0.942129887246715</v>
       </c>
-      <c r="K12" s="0" t="n">
+      <c r="K12" s="5" t="n">
         <v>1.02332975210129</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8"/>
+      <c r="B14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="8"/>
+      <c r="B15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="8"/>
+      <c r="B16" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -75570,4 +75601,190 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>851</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>852</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>853</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>854</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>855</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>1.83645150759808</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <f aca="false">C4/SUM($C$4:$C$8)</f>
+        <v>0.0178437422914117</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <f aca="false">(C4 - (B4*$C$8/$B$8))/(SUM($C$4:$C$8) + $C$8/$B$8)</f>
+        <v>0.0119072664654273</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>3.02367564775477</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>857</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>15.1163704271625</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <f aca="false">C5/SUM($C$4:$C$8)</f>
+        <v>0.146877070898861</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <f aca="false">(C5 - (B5*$C$8/$B$8))/(SUM($C$4:$C$8) + $C$8/$B$8)</f>
+        <v>0.108199091884514</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>3.82904002670742</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>858</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>7.20317866918906</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <f aca="false">C6/SUM($C$4:$C$8)</f>
+        <v>0.0699891411889832</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <f aca="false">(C6 - (B6*$C$8/$B$8))/(SUM($C$4:$C$8) + $C$8/$B$8)</f>
+        <v>0.0580152744111473</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>5.92993494201761</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>859</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>6.18331859813839</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <f aca="false">C7/SUM($C$4:$C$8)</f>
+        <v>0.0600797478802916</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <f aca="false">(C7 - (B7*$C$8/$B$8))/(SUM($C$4:$C$8) + $C$8/$B$8)</f>
+        <v>0.0510770242956365</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>6.78712897859321</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>860</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>239</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>72.579198539674</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <f aca="false">C8/SUM($C$4:$C$8)</f>
+        <v>0.705210297740452</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/Manuscript/Figures_for_Manuscript_files/saved_png/Supp.xlsx
+++ b/Manuscript/Figures_for_Manuscript_files/saved_png/Supp.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" state="visible" r:id="rId3"/>
@@ -20,6 +20,7 @@
     <sheet name="Chap1_Heatmap_topSpecies" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="Chap2_Alpha" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="Chap2_beta" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Chap2_DAA" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="331">
   <si>
     <t xml:space="preserve">Chap1: beta diversity, pairwise</t>
   </si>
@@ -1015,6 +1016,15 @@
   </si>
   <si>
     <t xml:space="preserve">Variance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LP1</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1035,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00E+00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1059,11 +1069,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1108,7 +1113,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1138,10 +1143,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1433,1227 +1434,1227 @@
   <dimension ref="A1:C111"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="22.12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="6" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="6" t="n">
         <v>0.0687022900763359</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="6" t="n">
         <v>0.169133441165051</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="6" t="n">
         <v>0.595419847328244</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="6" t="n">
         <v>0.164145792448626</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="6" t="n">
         <v>0.763358778625954</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="6" t="n">
         <v>0.0519146147077582</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="6" t="n">
         <v>0.0648854961832061</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="6" t="n">
         <v>0.0316334599690211</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="6" t="n">
         <v>0.083969465648855</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="6" t="n">
         <v>0.0279544004550394</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.786259541984733</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="6" t="n">
         <v>0.0254628047155567</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="6" t="n">
         <v>0.351145038167939</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="6" t="n">
         <v>0.018583170128798</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="6" t="n">
         <v>0.774809160305344</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="6" t="n">
         <v>0.0179314662968497</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="6" t="n">
         <v>0.461832061068702</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="6" t="n">
         <v>0.0137316900167408</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="6" t="n">
         <v>0.225190839694656</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="6" t="n">
         <v>0.0128182906304913</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="6" t="n">
         <v>0.347328244274809</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="6" t="n">
         <v>0.0123695582493242</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="6" t="n">
         <v>0.729007633587786</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="6" t="n">
         <v>0.0122291552693712</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="6" t="n">
         <v>0.675572519083969</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="6" t="n">
         <v>0.0120100263328018</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="6" t="n">
         <v>0.286259541984733</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="6" t="n">
         <v>0.00996404290826498</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="6" t="n">
         <v>0.687022900763359</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="6" t="n">
         <v>0.00940577391654725</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="6" t="n">
         <v>0.305343511450382</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="6" t="n">
         <v>0.00868620864428833</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="6" t="n">
         <v>0.152671755725191</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="6" t="n">
         <v>0.00848212288414241</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="6" t="n">
         <v>0.099236641221374</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="6" t="n">
         <v>0.0080176230254647</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="6" t="n">
         <v>0.270992366412214</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="6" t="n">
         <v>0.00782195030102232</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="6" t="n">
         <v>0.0877862595419847</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21" s="6" t="n">
         <v>0.0077998312601329</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="6" t="n">
         <v>0.656488549618321</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C22" s="6" t="n">
         <v>0.00713843293671163</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="6" t="n">
         <v>0.690839694656489</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="6" t="n">
         <v>0.0068038058344904</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="6" t="n">
         <v>0.767175572519084</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="6" t="n">
         <v>0.00659403709658449</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="6" t="n">
         <v>0.278625954198473</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25" s="6" t="n">
         <v>0.00553321458138434</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="6" t="n">
         <v>0.50763358778626</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26" s="6" t="n">
         <v>0.00543537821916315</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="6" t="n">
         <v>0.244274809160305</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C27" s="6" t="n">
         <v>0.00542111505929491</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="6" t="n">
         <v>0.435114503816794</v>
       </c>
-      <c r="C28" s="0" t="n">
+      <c r="C28" s="6" t="n">
         <v>0.004869197630956</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="6" t="n">
         <v>0.118320610687023</v>
       </c>
-      <c r="C29" s="0" t="n">
+      <c r="C29" s="6" t="n">
         <v>0.0045390277661936</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="6" t="n">
         <v>0.0954198473282443</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30" s="6" t="n">
         <v>0.00444977158608065</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="6" t="n">
         <v>0.614503816793893</v>
       </c>
-      <c r="C31" s="0" t="n">
+      <c r="C31" s="6" t="n">
         <v>0.0042039549402265</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="6" t="n">
         <v>0.290076335877863</v>
       </c>
-      <c r="C32" s="0" t="n">
+      <c r="C32" s="6" t="n">
         <v>0.00411442018277237</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="6" t="n">
         <v>0.282442748091603</v>
       </c>
-      <c r="C33" s="0" t="n">
+      <c r="C33" s="6" t="n">
         <v>0.00386715493474409</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="6" t="n">
         <v>0.67175572519084</v>
       </c>
-      <c r="C34" s="0" t="n">
+      <c r="C34" s="6" t="n">
         <v>0.00376541848974643</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="6" t="n">
         <v>0.0801526717557252</v>
       </c>
-      <c r="C35" s="0" t="n">
+      <c r="C35" s="6" t="n">
         <v>0.00374146083840525</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="6" t="n">
         <v>0.717557251908397</v>
       </c>
-      <c r="C36" s="0" t="n">
+      <c r="C36" s="6" t="n">
         <v>0.00363075420302171</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="6" t="n">
         <v>0.431297709923664</v>
       </c>
-      <c r="C37" s="0" t="n">
+      <c r="C37" s="6" t="n">
         <v>0.0036004449883017</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="6" t="n">
         <v>0.0763358778625954</v>
       </c>
-      <c r="C38" s="0" t="n">
+      <c r="C38" s="6" t="n">
         <v>0.00352818202600051</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="6" t="n">
         <v>0.187022900763359</v>
       </c>
-      <c r="C39" s="0" t="n">
+      <c r="C39" s="6" t="n">
         <v>0.00340059360374167</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="6" t="n">
         <v>0.236641221374046</v>
       </c>
-      <c r="C40" s="0" t="n">
+      <c r="C40" s="6" t="n">
         <v>0.00330119720840989</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="6" t="n">
         <v>0.0572519083969466</v>
       </c>
-      <c r="C41" s="0" t="n">
+      <c r="C41" s="6" t="n">
         <v>0.00322804279861694</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" s="6" t="n">
         <v>0.16030534351145</v>
       </c>
-      <c r="C42" s="0" t="n">
+      <c r="C42" s="6" t="n">
         <v>0.00314853682544517</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="6" t="n">
         <v>0.0725190839694656</v>
       </c>
-      <c r="C43" s="0" t="n">
+      <c r="C43" s="6" t="n">
         <v>0.00310775310269692</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="B44" s="0" t="n">
+      <c r="B44" s="6" t="n">
         <v>0.217557251908397</v>
       </c>
-      <c r="C44" s="0" t="n">
+      <c r="C44" s="6" t="n">
         <v>0.00302161698880515</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45" s="6" t="n">
         <v>0.729007633587786</v>
       </c>
-      <c r="C45" s="0" t="n">
+      <c r="C45" s="6" t="n">
         <v>0.00295659703737455</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="B46" s="0" t="n">
+      <c r="B46" s="6" t="n">
         <v>0.148854961832061</v>
       </c>
-      <c r="C46" s="0" t="n">
+      <c r="C46" s="6" t="n">
         <v>0.0029550927197322</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B47" s="6" t="n">
         <v>0.50381679389313</v>
       </c>
-      <c r="C47" s="0" t="n">
+      <c r="C47" s="6" t="n">
         <v>0.00295498128879573</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B48" s="0" t="n">
+      <c r="B48" s="6" t="n">
         <v>0.393129770992366</v>
       </c>
-      <c r="C48" s="0" t="n">
+      <c r="C48" s="6" t="n">
         <v>0.00295392269489925</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="B49" s="0" t="n">
+      <c r="B49" s="6" t="n">
         <v>0.469465648854962</v>
       </c>
-      <c r="C49" s="0" t="n">
+      <c r="C49" s="6" t="n">
         <v>0.00283140438024982</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B50" s="0" t="n">
+      <c r="B50" s="6" t="n">
         <v>0.156488549618321</v>
       </c>
-      <c r="C50" s="0" t="n">
+      <c r="C50" s="6" t="n">
         <v>0.00250173595470154</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="B51" s="0" t="n">
+      <c r="B51" s="6" t="n">
         <v>0.580152671755725</v>
       </c>
-      <c r="C51" s="0" t="n">
+      <c r="C51" s="6" t="n">
         <v>0.00239604371145917</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="B52" s="0" t="n">
+      <c r="B52" s="6" t="n">
         <v>0.274809160305344</v>
       </c>
-      <c r="C52" s="0" t="n">
+      <c r="C52" s="6" t="n">
         <v>0.00238161340518623</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B53" s="0" t="n">
+      <c r="B53" s="6" t="n">
         <v>0.267175572519084</v>
       </c>
-      <c r="C53" s="0" t="n">
+      <c r="C53" s="6" t="n">
         <v>0.00235888149414623</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="B54" s="0" t="n">
+      <c r="B54" s="6" t="n">
         <v>0.175572519083969</v>
       </c>
-      <c r="C54" s="0" t="n">
+      <c r="C54" s="6" t="n">
         <v>0.00224951203000033</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="6" t="n">
         <v>0.232824427480916</v>
       </c>
-      <c r="C55" s="0" t="n">
+      <c r="C55" s="6" t="n">
         <v>0.00205356072821677</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="6" t="n">
         <v>0.213740458015267</v>
       </c>
-      <c r="C56" s="0" t="n">
+      <c r="C56" s="6" t="n">
         <v>0.00200480969351088</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="6" t="n">
         <v>0.450381679389313</v>
       </c>
-      <c r="C57" s="0" t="n">
+      <c r="C57" s="6" t="n">
         <v>0.00197672909752029</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="B58" s="0" t="n">
+      <c r="B58" s="6" t="n">
         <v>0.0687022900763359</v>
       </c>
-      <c r="C58" s="0" t="n">
+      <c r="C58" s="6" t="n">
         <v>0.00196458312544499</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="B59" s="0" t="n">
+      <c r="B59" s="6" t="n">
         <v>0.709923664122137</v>
       </c>
-      <c r="C59" s="0" t="n">
+      <c r="C59" s="6" t="n">
         <v>0.00196374739342146</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="B60" s="0" t="n">
+      <c r="B60" s="6" t="n">
         <v>0.50381679389313</v>
       </c>
-      <c r="C60" s="0" t="n">
+      <c r="C60" s="6" t="n">
         <v>0.00195483291850381</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="B61" s="0" t="n">
+      <c r="B61" s="6" t="n">
         <v>0.580152671755725</v>
       </c>
-      <c r="C61" s="0" t="n">
+      <c r="C61" s="6" t="n">
         <v>0.00194842563965675</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="B62" s="0" t="n">
+      <c r="B62" s="6" t="n">
         <v>0.290076335877863</v>
       </c>
-      <c r="C62" s="0" t="n">
+      <c r="C62" s="6" t="n">
         <v>0.00191872929508734</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="B63" s="0" t="n">
+      <c r="B63" s="6" t="n">
         <v>0.209923664122137</v>
       </c>
-      <c r="C63" s="0" t="n">
+      <c r="C63" s="6" t="n">
         <v>0.00170896055718143</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="B64" s="0" t="n">
+      <c r="B64" s="6" t="n">
         <v>0.0763358778625954</v>
       </c>
-      <c r="C64" s="0" t="n">
+      <c r="C64" s="6" t="n">
         <v>0.00167502983702613</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B65" s="0" t="n">
+      <c r="B65" s="6" t="n">
         <v>0.103053435114504</v>
       </c>
-      <c r="C65" s="0" t="n">
+      <c r="C65" s="6" t="n">
         <v>0.00162070725549671</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="B66" s="0" t="n">
+      <c r="B66" s="6" t="n">
         <v>0.152671755725191</v>
       </c>
-      <c r="C66" s="0" t="n">
+      <c r="C66" s="6" t="n">
         <v>0.00157919923166141</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="B67" s="0" t="n">
+      <c r="B67" s="6" t="n">
         <v>0.412213740458015</v>
       </c>
-      <c r="C67" s="0" t="n">
+      <c r="C67" s="6" t="n">
         <v>0.00156415605523788</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="B68" s="0" t="n">
+      <c r="B68" s="6" t="n">
         <v>0.0534351145038168</v>
       </c>
-      <c r="C68" s="0" t="n">
+      <c r="C68" s="6" t="n">
         <v>0.00154766427664023</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="B69" s="0" t="n">
+      <c r="B69" s="6" t="n">
         <v>0.240458015267176</v>
       </c>
-      <c r="C69" s="0" t="n">
+      <c r="C69" s="6" t="n">
         <v>0.00153741263048493</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B70" s="0" t="n">
+      <c r="B70" s="6" t="n">
         <v>0.358778625954198</v>
       </c>
-      <c r="C70" s="0" t="n">
+      <c r="C70" s="6" t="n">
         <v>0.00152632525230611</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="B71" s="0" t="n">
+      <c r="B71" s="6" t="n">
         <v>0.251908396946565</v>
       </c>
-      <c r="C71" s="0" t="n">
+      <c r="C71" s="6" t="n">
         <v>0.00151456928850846</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="B72" s="0" t="n">
+      <c r="B72" s="6" t="n">
         <v>0.324427480916031</v>
       </c>
-      <c r="C72" s="0" t="n">
+      <c r="C72" s="6" t="n">
         <v>0.0015035933412661</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="B73" s="0" t="n">
+      <c r="B73" s="6" t="n">
         <v>0.0534351145038168</v>
       </c>
-      <c r="C73" s="0" t="n">
+      <c r="C73" s="6" t="n">
         <v>0.00150186616175081</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="B74" s="0" t="n">
+      <c r="B74" s="6" t="n">
         <v>0.637404580152672</v>
       </c>
-      <c r="C74" s="0" t="n">
+      <c r="C74" s="6" t="n">
         <v>0.00145656948607551</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="B75" s="0" t="n">
+      <c r="B75" s="6" t="n">
         <v>0.370229007633588</v>
       </c>
-      <c r="C75" s="0" t="n">
+      <c r="C75" s="6" t="n">
         <v>0.00140843132152021</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="B76" s="0" t="n">
+      <c r="B76" s="6" t="n">
         <v>0.0687022900763359</v>
       </c>
-      <c r="C76" s="0" t="n">
+      <c r="C76" s="6" t="n">
         <v>0.00140753987402844</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="B77" s="0" t="n">
+      <c r="B77" s="6" t="n">
         <v>0.354961832061069</v>
       </c>
-      <c r="C77" s="0" t="n">
+      <c r="C77" s="6" t="n">
         <v>0.00139338814509667</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B78" s="0" t="n">
+      <c r="B78" s="6" t="n">
         <v>0.400763358778626</v>
       </c>
-      <c r="C78" s="0" t="n">
+      <c r="C78" s="6" t="n">
         <v>0.00138826232201903</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="B79" s="0" t="n">
+      <c r="B79" s="6" t="n">
         <v>0.0801526717557252</v>
       </c>
-      <c r="C79" s="0" t="n">
+      <c r="C79" s="6" t="n">
         <v>0.00136224319835314</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="A80" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="B80" s="0" t="n">
+      <c r="B80" s="6" t="n">
         <v>0.16412213740458</v>
       </c>
-      <c r="C80" s="0" t="n">
+      <c r="C80" s="6" t="n">
         <v>0.00135750738355314</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="B81" s="0" t="n">
+      <c r="B81" s="6" t="n">
         <v>0.0801526717557252</v>
       </c>
-      <c r="C81" s="0" t="n">
+      <c r="C81" s="6" t="n">
         <v>0.0013178379701696</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="B82" s="0" t="n">
+      <c r="B82" s="6" t="n">
         <v>0.0877862595419847</v>
       </c>
-      <c r="C82" s="0" t="n">
+      <c r="C82" s="6" t="n">
         <v>0.00129454890444725</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="B83" s="0" t="n">
+      <c r="B83" s="6" t="n">
         <v>0.232824427480916</v>
       </c>
-      <c r="C83" s="0" t="n">
+      <c r="C83" s="6" t="n">
         <v>0.00129449318897901</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="B84" s="0" t="n">
+      <c r="B84" s="6" t="n">
         <v>0.263358778625954</v>
       </c>
-      <c r="C84" s="0" t="n">
+      <c r="C84" s="6" t="n">
         <v>0.00129304458680489</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="B85" s="0" t="n">
+      <c r="B85" s="6" t="n">
         <v>0.221374045801527</v>
       </c>
-      <c r="C85" s="0" t="n">
+      <c r="C85" s="6" t="n">
         <v>0.00125844528103077</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="B86" s="0" t="n">
+      <c r="B86" s="6" t="n">
         <v>0.209923664122137</v>
       </c>
-      <c r="C86" s="0" t="n">
+      <c r="C86" s="6" t="n">
         <v>0.00125064511547783</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="B87" s="0" t="n">
+      <c r="B87" s="6" t="n">
         <v>0.541984732824428</v>
       </c>
-      <c r="C87" s="0" t="n">
+      <c r="C87" s="6" t="n">
         <v>0.00122947323754841</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="B88" s="0" t="n">
+      <c r="B88" s="6" t="n">
         <v>0.213740458015267</v>
       </c>
-      <c r="C88" s="0" t="n">
+      <c r="C88" s="6" t="n">
         <v>0.0012251831464943</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="B89" s="0" t="n">
+      <c r="B89" s="6" t="n">
         <v>0.0687022900763359</v>
       </c>
-      <c r="C89" s="0" t="n">
+      <c r="C89" s="6" t="n">
         <v>0.00122484885368488</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="B90" s="0" t="n">
+      <c r="B90" s="6" t="n">
         <v>0.33587786259542</v>
       </c>
-      <c r="C90" s="0" t="n">
+      <c r="C90" s="6" t="n">
         <v>0.00121911016045665</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="B91" s="0" t="n">
+      <c r="B91" s="6" t="n">
         <v>0.137404580152672</v>
       </c>
-      <c r="C91" s="0" t="n">
+      <c r="C91" s="6" t="n">
         <v>0.00121794013562371</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="B92" s="0" t="n">
+      <c r="B92" s="6" t="n">
         <v>0.706106870229008</v>
       </c>
-      <c r="C92" s="0" t="n">
+      <c r="C92" s="6" t="n">
         <v>0.00120306410560488</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="B93" s="0" t="n">
+      <c r="B93" s="6" t="n">
         <v>0.0725190839694656</v>
       </c>
-      <c r="C93" s="0" t="n">
+      <c r="C93" s="6" t="n">
         <v>0.00119548680192488</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="B94" s="0" t="n">
+      <c r="B94" s="6" t="n">
         <v>0.202290076335878</v>
       </c>
-      <c r="C94" s="0" t="n">
+      <c r="C94" s="6" t="n">
         <v>0.00119253388210841</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="B95" s="0" t="n">
+      <c r="B95" s="6" t="n">
         <v>0.683206106870229</v>
       </c>
-      <c r="C95" s="0" t="n">
+      <c r="C95" s="6" t="n">
         <v>0.00118696233528488</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="A96" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="B96" s="0" t="n">
+      <c r="B96" s="6" t="n">
         <v>0.225190839694656</v>
       </c>
-      <c r="C96" s="0" t="n">
+      <c r="C96" s="6" t="n">
         <v>0.00118495657842841</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="A97" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="B97" s="0" t="n">
+      <c r="B97" s="6" t="n">
         <v>0.083969465648855</v>
       </c>
-      <c r="C97" s="0" t="n">
+      <c r="C97" s="6" t="n">
         <v>0.00117698926647076</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
+      <c r="A98" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="B98" s="0" t="n">
+      <c r="B98" s="6" t="n">
         <v>0.0801526717557252</v>
       </c>
-      <c r="C98" s="0" t="n">
+      <c r="C98" s="6" t="n">
         <v>0.00116517758720488</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
+      <c r="A99" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="B99" s="0" t="n">
+      <c r="B99" s="6" t="n">
         <v>0.183206106870229</v>
       </c>
-      <c r="C99" s="0" t="n">
+      <c r="C99" s="6" t="n">
         <v>0.00114461857942605</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="A100" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="B100" s="0" t="n">
+      <c r="B100" s="6" t="n">
         <v>0.278625954198473</v>
       </c>
-      <c r="C100" s="0" t="n">
+      <c r="C100" s="6" t="n">
         <v>0.00113609411278605</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="B101" s="0" t="n">
+      <c r="B101" s="6" t="n">
         <v>0.137404580152672</v>
       </c>
-      <c r="C101" s="0" t="n">
+      <c r="C101" s="6" t="n">
         <v>0.00111776372373663</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="B102" s="0" t="n">
+      <c r="B102" s="6" t="n">
         <v>0.0801526717557252</v>
       </c>
-      <c r="C102" s="0" t="n">
+      <c r="C102" s="6" t="n">
         <v>0.00111742943092722</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="B103" s="0" t="n">
+      <c r="B103" s="6" t="n">
         <v>0.351145038167939</v>
       </c>
-      <c r="C103" s="0" t="n">
+      <c r="C103" s="6" t="n">
         <v>0.00108244011687545</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="B104" s="0" t="n">
+      <c r="B104" s="6" t="n">
         <v>0.538167938931298</v>
       </c>
-      <c r="C104" s="0" t="n">
+      <c r="C104" s="6" t="n">
         <v>0.00107029414480016</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="A105" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="B105" s="0" t="n">
+      <c r="B105" s="6" t="n">
         <v>0.465648854961832</v>
       </c>
-      <c r="C105" s="0" t="n">
+      <c r="C105" s="6" t="n">
         <v>0.00105759101804251</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
+      <c r="A106" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="B106" s="0" t="n">
+      <c r="B106" s="6" t="n">
         <v>0.385496183206107</v>
       </c>
-      <c r="C106" s="0" t="n">
+      <c r="C106" s="6" t="n">
         <v>0.00105564097665427</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
+      <c r="A107" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="B107" s="0" t="n">
+      <c r="B107" s="6" t="n">
         <v>0.347328244274809</v>
       </c>
-      <c r="C107" s="0" t="n">
+      <c r="C107" s="6" t="n">
         <v>0.00105486096009898</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="s">
+      <c r="A108" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="B108" s="0" t="n">
+      <c r="B108" s="6" t="n">
         <v>0.049618320610687</v>
       </c>
-      <c r="C108" s="0" t="n">
+      <c r="C108" s="6" t="n">
         <v>0.00103931634446133</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
+      <c r="A109" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="B109" s="0" t="n">
+      <c r="B109" s="6" t="n">
         <v>0.137404580152672</v>
       </c>
-      <c r="C109" s="0" t="n">
+      <c r="C109" s="6" t="n">
         <v>0.00103686486385897</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="s">
+      <c r="A110" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B110" s="0" t="n">
+      <c r="B110" s="6" t="n">
         <v>0.122137404580153</v>
       </c>
-      <c r="C110" s="0" t="n">
+      <c r="C110" s="6" t="n">
         <v>0.00102042880072956</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
+      <c r="A111" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="B111" s="0" t="n">
+      <c r="B111" s="6" t="n">
         <v>0.469465648854962</v>
       </c>
-      <c r="C111" s="0" t="n">
+      <c r="C111" s="6" t="n">
         <v>0.00101898019855544</v>
       </c>
     </row>
@@ -2676,136 +2677,136 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="15.99"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="6" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="6" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="6" t="n">
         <v>0.276660002455725</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="6" t="n">
         <v>1.31871793394639</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="6" t="n">
         <v>1.17438172716505</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="6" t="n">
         <v>1.48079363726972</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="3" t="n">
         <v>2.8995008094107E-006</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="6" t="n">
         <v>-0.0322655474052416</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="6" t="n">
         <v>0.968249431813671</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="6" t="n">
         <v>0.86256944135718</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="6" t="n">
         <v>1.08687708752168</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="6" t="n">
         <v>0.584258112756577</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="6" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="6" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="6" t="n">
         <v>0.552290628788466</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="6" t="n">
         <v>1.73722780777394</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="6" t="n">
         <v>1.53693730399194</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="6" t="n">
         <v>1.96361975746466</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="3" t="n">
         <v>2.44011783097304E-007</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="6" t="n">
         <v>-0.0550393576729069</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="6" t="n">
         <v>0.946447897233675</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="6" t="n">
         <v>0.837328917390006</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="6" t="n">
         <v>1.06978703777505</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="6" t="n">
         <v>0.349430090479403</v>
       </c>
     </row>
@@ -2829,198 +2830,757 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>0.0484526152732806</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0.742451654769916</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>0.0503614780062512</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0.441378631784566</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>11.8668822977777</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.458767398450536</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.0323683047339711</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.612745551913795</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.0419322672619551</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.527130775266577</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>30.1478446889113</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.682883726291707</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>12.7117686197841</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.986462345614966</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.0658235628172518</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>41.3691575014349</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>3.81660298113778</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.214216087386488</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>324</v>
+        <v>13</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>178</v>
+        <v>29</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>3.81148972130375</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.368110656289552</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>1.19966144957483E-007</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>1.1893786371499E-005</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>10</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>1</v>
+        <v>-3.39149279705819</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.0484526152732806</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>0.742451654769916</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F3" s="0" t="n">
-        <v>0.0503614780062512</v>
+        <v>0.229769364882277</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>1.68360045972696E-009</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>3.89472906350169E-007</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>1</v>
+        <v>3.31815183132703</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.441378631784566</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>11.8668822977777</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>0.458767398450536</v>
+        <v>0.362898101901437</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>5.03256238863041E-007</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>3.88066477523278E-005</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-3.23165310923982</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.358081616134054</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>5.83595233433058E-007</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>4.05015092002542E-005</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>325</v>
+      <c r="A6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>-3.19580343854298</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.259171310279819</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1.50704184527379E-008</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>2.61471760155002E-006</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>178</v>
+        <v>36</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>-3.0323154717027</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.492245732122077</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>3.43122543349245E-005</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.0017009074648884</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>10</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>1</v>
+        <v>-2.57599012180562</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.0323683047339711</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <v>0.612745551913795</v>
-      </c>
-      <c r="E8" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F8" s="0" t="n">
-        <v>0.0419322672619551</v>
+        <v>0.328749338087185</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>2.80436277024324E-006</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>0.00016218564687906</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>1</v>
+        <v>-2.51953877383423</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.527130775266577</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>30.1478446889113</v>
-      </c>
-      <c r="E9" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F9" s="0" t="n">
-        <v>0.682883726291707</v>
+        <v>0.36215788996766</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>9.96146072419514E-006</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0.00053178874943011</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>2.42946874757561</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>0.284012489662603</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1.06623421356753E-006</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>6.72696858378063E-005</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>326</v>
+        <v>37</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>-2.41745356288511</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>0.399836526035275</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>4.12497516120456E-005</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>0.00190848850791731</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>327</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>178</v>
+        <v>46</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>2.39789340597254</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>0.554667475288224</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0.00082709791841563</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>0.0239169148075186</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>10</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>1</v>
+        <v>2.3219097547748</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>12.7117686197841</v>
-      </c>
-      <c r="D13" s="0" t="n">
-        <v>0.986462345614966</v>
+        <v>0.455300453731415</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0.00020383911999802</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="F13" s="0" t="n">
-        <v>0.0658235628172518</v>
+        <v>0.00707321746393155</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>1</v>
+        <v>2.24473644610638</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>41.3691575014349</v>
-      </c>
-      <c r="D14" s="0" t="n">
-        <v>3.81660298113778</v>
+        <v>0.410837990224907</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>0.00010863507948459</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F14" s="0" t="n">
-        <v>0.214216087386488</v>
+        <v>0.00443486736248887</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>2.19418601391856</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>0.503753385684628</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>0.00077879060618256</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>0.0238970126779331</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>-2.12760594700637</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>0.222488878043511</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>3.01496379293157E-007</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>2.61548109036814E-005</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>2.03554842627889</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>0.0484484464833779</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>2.8425181253039E-015</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>1.97270757896091E-012</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>-2.02073689695941</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>0.340396650164552</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>4.93250495451147E-005</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>0.00213947402401935</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>-1.93618920251031</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>0.490643490005679</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>0.00167342443445489</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>0.0446675599042958</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>-1.80073789040321</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>0.365280202410378</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0.00027515332955387</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>0.00909316241478042</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>-1.71967153863296</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>0.395637269791286</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>0.00079197592448481</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>0.0238970126779331</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>-1.71101019241411</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>0.398285711611776</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0.00086979677647775</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>0.0241455585150224</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>-0.993687874926557</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>0.185882084098689</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>0.00013295112314791</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>0.00512600441470282</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>-0.987254843069378</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>0.19247654304813</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0.00019357769675594</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>0.00707068008150661</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>0.921662350544331</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>0.04966790469928</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>9.75342765932603E-011</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>3.38443939778613E-008</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>-0.766436200678925</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>0.073616086818163</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>1.12498913563331E-007</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>1.1893786371499E-005</v>
+      </c>
+      <c r="F26" s="0" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>-0.639318485742424</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>0.060556903589545</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>9.55576688732331E-008</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>1.1893786371499E-005</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -4974,10 +5534,10 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8.95"/>
@@ -7315,343 +7875,343 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="6" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="6" t="n">
         <v>5134397</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="6" t="n">
         <v>28.6065332960931</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="6" t="n">
         <v>3035664</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="6" t="n">
         <v>45.5198774125982</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="6" t="n">
         <v>1034676</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="6" t="n">
         <v>51.2846231937811</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="6" t="n">
         <v>605995</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="6" t="n">
         <v>54.6609527111063</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="6" t="n">
         <v>593031</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="6" t="n">
         <v>57.9650526954113</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="6" t="n">
         <v>583338</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="6" t="n">
         <v>61.2151476763558</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="6" t="n">
         <v>506091</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="6" t="n">
         <v>64.034857379823</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="6" t="n">
         <v>482878</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="6" t="n">
         <v>66.7252347668756</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="6" t="n">
         <v>373869</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="6" t="n">
         <v>68.8082634062421</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="6" t="n">
         <v>367958</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="6" t="n">
         <v>70.8583586323346</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="6" t="n">
         <v>295277</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="6" t="n">
         <v>72.5035082637461</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="6" t="n">
         <v>247026</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="6" t="n">
         <v>73.8798251893755</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="6" t="n">
         <v>195094</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="6" t="n">
         <v>74.9668005453653</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="6" t="n">
         <v>192174</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="6" t="n">
         <v>76.0375069846304</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="6" t="n">
         <v>149080</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="6" t="n">
         <v>76.8681131850823</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="6" t="n">
         <v>146140</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="6" t="n">
         <v>77.682339037873</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="6" t="n">
         <v>140391</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="6" t="n">
         <v>78.4645340679752</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="6" t="n">
         <v>139994</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="6" t="n">
         <v>79.2445171939885</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="6" t="n">
         <v>126861</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="6" t="n">
         <v>79.9513291955684</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="6" t="n">
         <v>125426</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21" s="6" t="n">
         <v>80.6501460274565</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="6" t="n">
         <v>121398</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C22" s="6" t="n">
         <v>81.3265206687394</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="6" t="n">
         <v>93657</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="6" t="n">
         <v>81.8483350295908</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="6" t="n">
         <v>91813</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="6" t="n">
         <v>82.3598754580995</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="6" t="n">
         <v>89796</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25" s="6" t="n">
         <v>82.8601780766653</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="6" t="n">
         <v>82573</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26" s="6" t="n">
         <v>83.3202374125246</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="6" t="n">
         <v>82192</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C27" s="6" t="n">
         <v>83.7781739890442</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="6" t="n">
         <v>80882</v>
       </c>
-      <c r="C28" s="0" t="n">
+      <c r="C28" s="6" t="n">
         <v>84.228811839225</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="6" t="n">
         <v>78431</v>
       </c>
-      <c r="C29" s="0" t="n">
+      <c r="C29" s="6" t="n">
         <v>84.6657938281413</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="6" t="n">
         <v>73386</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30" s="6" t="n">
         <v>85.0746673633329</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="6" t="n">
         <v>70440</v>
       </c>
-      <c r="C31" s="0" t="n">
+      <c r="C31" s="6" t="n">
         <v>85.4671271215824</v>
       </c>
     </row>
